--- a/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Downtown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Apple Cider (Gal)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Natalie's - Grapefruit</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>13.25</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>26.50</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.5</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Natalie's - Honey Tangerine</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>14.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Natalie's - Lemonade</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9.25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>9.25</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.25</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Natalie's - Orange Juice</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.75</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Natalie's - Orange Mango</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Natalie's - Orange Pineapple</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Red Jacket - Fuji Apple</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11.25</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Red Jacket - Rasp/Apple</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.25</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Red Jacket - Strawberry (12oz)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11.25</v>
       </c>
     </row>
   </sheetData>
